--- a/data/trans_dic/IP07C31_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP07C31_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -548,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -588,7 +589,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -598,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -638,7 +639,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8-11</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,44 +672,273 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A6:A7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
+          <t>n</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -716,90 +946,61 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>IC 95%</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0; 1,09</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0; 1,02</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,71</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,62</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+  <mergeCells count="4">
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A4:A6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
